--- a/kb023_information.xlsx
+++ b/kb023_information.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{073FF6CD-03B9-4787-B22A-2F83BB2F58CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5BB6E74-0D2E-4089-BD10-8744F9F2D1D3}"/>
+    <workbookView xWindow="4155" yWindow="4155" windowWidth="21600" windowHeight="11295" xr2:uid="{D5BB6E74-0D2E-4089-BD10-8744F9F2D1D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/kb023_information.xlsx
+++ b/kb023_information.xlsx
@@ -1,196 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Cursor/KB023/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{073FF6CD-03B9-4787-B22A-2F83BB2F58CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="4155" windowWidth="21600" windowHeight="11295" xr2:uid="{D5BB6E74-0D2E-4089-BD10-8744F9F2D1D3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6555" yWindow="2460" windowWidth="28320" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
-  <si>
-    <t>배정일자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>문자전송</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DB종류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가능상품</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타겟상품</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>계약자명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주민번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연락처</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>직업</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>피보험자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>동의</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>db1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가능1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타겟1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>김찬식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>610623-1010432</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-3003-5600</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>회사원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>인천광역시 연수구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>정경희</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부동의</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>db2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타켓2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>600517-2067915</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-9631-5900</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -333,63 +199,171 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -709,128 +683,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83C2A59C-0C61-4D52-A729-EC7E71472712}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
+    <col width="11.125" customWidth="1" style="15" min="2" max="2"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
+    <col width="8.125" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="15" min="5" max="7"/>
+    <col width="15.875" bestFit="1" customWidth="1" style="15" min="8" max="8"/>
+    <col width="14.375" bestFit="1" customWidth="1" style="15" min="9" max="9"/>
+    <col width="7.125" bestFit="1" customWidth="1" style="15" min="10" max="10"/>
+    <col width="17.875" bestFit="1" customWidth="1" style="15" min="11" max="11"/>
+    <col width="9.25" bestFit="1" customWidth="1" style="15" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>배정일자</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>종료일자</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>문자전송</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>DB종류</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>가능상품</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>타겟상품</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>계약자명</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>주민번호</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>직업</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>피보험자</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2">
+      <c r="A2" s="4" t="n">
         <v>46080</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>46081</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>15</v>
+      <c r="B2" s="13" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>비동의</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>db1</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>김찬식</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>6106231010432</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>010-3003-5600</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>회사원</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>정경희</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>